--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/MICHIGAN_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/MICHIGAN_2015.xlsx
@@ -1950,7 +1950,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C89">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C128">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C220">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C563">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C623">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C624">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C639">
